--- a/data/chinese/P2T3_Chapter13.xlsx
+++ b/data/chinese/P2T3_Chapter13.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8207C7F5-A439-5D4B-86FC-182A6AFF88BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8561B6FA-5558-6E4E-8DAE-2F545E210825}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -56,112 +56,151 @@
     <t>航行</t>
   </si>
   <si>
-    <t>船或飛機等在水上、空中行駛</t>
-  </si>
-  <si>
-    <t>太空船在宇宙中平穩地航行。</t>
-  </si>
-  <si>
     <t>必須</t>
   </si>
   <si>
-    <t>一定要、表示事理上的必要</t>
-  </si>
-  <si>
-    <t>我們在太空中必須遵守安全規則。</t>
-  </si>
-  <si>
     <t>解決</t>
   </si>
   <si>
-    <t>處理問題，使有結果</t>
-  </si>
-  <si>
-    <t>科學家想辦法解決太空生活的難題。</t>
-  </si>
-  <si>
     <t>特殊</t>
   </si>
   <si>
-    <t>與一般不同、特別的</t>
-  </si>
-  <si>
-    <t>太空站裡有特殊的設備幫助宇航員生活。</t>
-  </si>
-  <si>
     <t>平穩</t>
   </si>
   <si>
-    <t>穩定、沒有波動或晃動</t>
-  </si>
-  <si>
-    <t>飛船平穩地進入了預定軌道。</t>
-  </si>
-  <si>
     <t>綁在</t>
   </si>
   <si>
-    <t>用繩子等固定在某個地方</t>
-  </si>
-  <si>
-    <t>宇航員把睡袋綁在艙壁上睡覺。</t>
-  </si>
-  <si>
     <t>牢牢</t>
   </si>
   <si>
-    <t>牢固、穩固地</t>
-  </si>
-  <si>
-    <t>物品要牢牢固定，不然會飄浮起來。</t>
-  </si>
-  <si>
     <t>安穩</t>
   </si>
   <si>
-    <t>平穩安定、沒有危險或晃動</t>
-  </si>
-  <si>
-    <t>宇航員在睡袋裡睡得很安穩。</t>
-  </si>
-  <si>
     <t>飄浮</t>
   </si>
   <si>
-    <t>在空中或液體中浮動不定</t>
-  </si>
-  <si>
-    <t>水滴會在太空艙裡飄浮，不會落下來。</t>
-  </si>
-  <si>
     <t>宇宙</t>
   </si>
   <si>
-    <t>包括地球在內的所有空間和萬物</t>
-  </si>
-  <si>
-    <t>宇宙中有許多我們還不知道的奧秘。</t>
-  </si>
-  <si>
     <t>有趣</t>
   </si>
   <si>
-    <t>有意思、能引起好奇或興趣</t>
-  </si>
-  <si>
-    <t>太空生活有很多有趣的現象，和地球不同。</t>
-  </si>
-  <si>
     <t>淋浴</t>
   </si>
   <si>
-    <t>用噴水的方式洗澡</t>
-  </si>
-  <si>
-    <t>宇航員在太空艙裡用特殊的方式淋浴。</t>
-  </si>
-  <si>
     <t>沒有必懂寫生字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>舟夜書所見〔清〕查慎行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月黑見漁燈,
+孤光一點螢。
+微微風簇浪,
+散作滿河星。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上沒有月亮，天很黑，只看見漁船上的一點燈光，像螢火蟲一樣。輕輕的風吹來，吹起了小波浪，把燈光晃成了好多好多點，看起來就像整條河都佈滿了星星，好漂亮呀！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>船、飛機在路上或空中向前行進。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一定要做，不能不做。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>把困難、問題處理好。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跟平常不一樣，很特別。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不會搖晃、顛簸，很安定。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用繩子等把東西繫在某個地方。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抓得、綁得很緊，不會鬆開。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安定平靜，沒有晃動。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>東西輕輕地浮在水面或空中，隨風移動。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包含所有星星、天空、地球的廣大空間。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很好玩、有意思，讓人喜歡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>站著用水沖洗身體，也就是沖澡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>運動完後，我會__________清洗身體。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>落葉在水面上__________，隨著水流移動。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遇到困難要想辦法__________。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>__________非常廣大，有許多星球。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請把行李__________車上，不要掉落。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上學__________準時到校，不可以遲到。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>車子開得很__________，一點也不顛簸。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輪船在大海上__________。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>他雙手__________抓住欄杆，十分安全。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這款玩具造型很__________，和別的不一樣。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>房間裡的東西擺放整齊，顯得很__________。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這個故事內容很__________，大家都愛聽。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -590,13 +629,13 @@
     </row>
     <row r="2" spans="1:11" ht="27">
       <c r="A2" s="7" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D2" s="7">
         <v>1</v>
@@ -841,7 +880,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="53.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="71.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -876,10 +915,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -891,13 +930,13 @@
     </row>
     <row r="3" spans="1:11" ht="27">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -906,13 +945,13 @@
     </row>
     <row r="4" spans="1:11" ht="27">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -921,13 +960,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -936,13 +975,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -951,13 +990,13 @@
     </row>
     <row r="7" spans="1:11" ht="27">
       <c r="A7" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -966,13 +1005,13 @@
     </row>
     <row r="8" spans="1:11" ht="27">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -981,13 +1020,13 @@
     </row>
     <row r="9" spans="1:11" ht="27">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -996,13 +1035,13 @@
     </row>
     <row r="10" spans="1:11" ht="27">
       <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="C10" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -1011,13 +1050,13 @@
     </row>
     <row r="11" spans="1:11" ht="27">
       <c r="A11" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -1026,13 +1065,13 @@
     </row>
     <row r="12" spans="1:11" ht="27">
       <c r="A12" s="3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -1041,13 +1080,13 @@
     </row>
     <row r="13" spans="1:11" ht="27">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D13" s="3">
         <v>3</v>
@@ -1201,31 +1240,43 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B55EBE-976A-904F-A78F-71BFD8B8303C}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="B2" s="6"/>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="80">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="B3" s="6"/>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="B4" s="6"/>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="B5" s="6"/>
     </row>
   </sheetData>
